--- a/Assets/Excel/Giftpack.xlsx
+++ b/Assets/Excel/Giftpack.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18810" windowHeight="7575"/>
+    <workbookView windowWidth="15825" windowHeight="9405"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
   <si>
     <t>id</t>
   </si>
@@ -77,27 +77,6 @@
   </si>
   <si>
     <t>礼包等级</t>
-  </si>
-  <si>
-    <t>StandardPack</t>
-  </si>
-  <si>
-    <t>RareGiftPack</t>
-  </si>
-  <si>
-    <t>LuxuryGiftPack</t>
-  </si>
-  <si>
-    <t>SilverGiftPack</t>
-  </si>
-  <si>
-    <t>GoldGiftPack</t>
-  </si>
-  <si>
-    <t>PlatinumGiftPack</t>
-  </si>
-  <si>
-    <t>DiamondGiftPack</t>
   </si>
 </sst>
 </file>
@@ -1115,11 +1094,11 @@
       <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>16</v>
+      <c r="B4" s="1">
+        <v>1</v>
       </c>
       <c r="C4" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D4" s="1">
         <v>1</v>
@@ -1128,7 +1107,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -1138,20 +1117,20 @@
       <c r="A5" s="1">
         <v>2</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>17</v>
+      <c r="B5" s="1">
+        <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="D5" s="1">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="E5" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F5" s="1">
-        <v>1181</v>
+        <v>1400</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1161,20 +1140,20 @@
       <c r="A6" s="1">
         <v>3</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
+      <c r="B6" s="1">
+        <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>376</v>
+        <v>500</v>
       </c>
       <c r="D6" s="1">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="E6" s="1">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F6" s="1">
-        <v>4702</v>
+        <v>5500</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -1184,8 +1163,8 @@
       <c r="A7" s="1">
         <v>4</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>19</v>
+      <c r="B7" s="1">
+        <v>4</v>
       </c>
       <c r="C7" s="1">
         <v>24</v>
@@ -1197,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="1">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1207,8 +1186,8 @@
       <c r="A8" s="1">
         <v>5</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>20</v>
+      <c r="B8" s="1">
+        <v>5</v>
       </c>
       <c r="C8" s="1">
         <v>48</v>
@@ -1217,10 +1196,10 @@
         <v>10</v>
       </c>
       <c r="E8" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" s="1">
-        <v>219</v>
+        <v>160</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1230,8 +1209,8 @@
       <c r="A9" s="1">
         <v>6</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>21</v>
+      <c r="B9" s="1">
+        <v>6</v>
       </c>
       <c r="C9" s="1">
         <v>64</v>
@@ -1240,37 +1219,22 @@
         <v>15</v>
       </c>
       <c r="E9" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F9" s="1">
-        <v>369</v>
+        <v>320</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="1">
-        <v>7</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="1">
-        <v>128</v>
-      </c>
-      <c r="D10" s="1">
-        <v>20</v>
-      </c>
-      <c r="E10" s="1">
-        <v>2</v>
-      </c>
-      <c r="F10" s="1">
-        <v>486</v>
-      </c>
-      <c r="G10">
-        <v>3</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
     </row>
     <row r="11" spans="1:7">
       <c r="B11" s="1"/>
